--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Tabela.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Tabela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD5E60F-D21E-4FA3-B43A-0EF465F119DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750D7CEE-91D0-42F6-A62E-755D92A36194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t>CONCESSIONÁRIA - 1º NIVEL</t>
   </si>
@@ -206,9 +206,6 @@
     <t>SIM</t>
   </si>
   <si>
-    <t>Relatório enviado ao parceiro</t>
-  </si>
-  <si>
     <t>Comprovante de pagamento</t>
   </si>
   <si>
@@ -224,42 +221,6 @@
     <t>Recibo do pagamento complementar</t>
   </si>
   <si>
-    <t>VIGENTE_venc:22/04/2027</t>
-  </si>
-  <si>
-    <t>CONCEIÇÃO</t>
-  </si>
-  <si>
-    <t>RECLAMAÇÃO 029/2025</t>
-  </si>
-  <si>
-    <t>Cobrança indevida - Enquadramento IP</t>
-  </si>
-  <si>
-    <t>Cobrança indevida</t>
-  </si>
-  <si>
-    <t>1693012-5</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>Em análise</t>
-  </si>
-  <si>
-    <t>010.597.08625-44</t>
-  </si>
-  <si>
-    <t>Em análise na agência</t>
-  </si>
-  <si>
-    <t>Memorial de cálculo não está em dobro completamento</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
     <t>Valor ajuste</t>
   </si>
   <si>
@@ -267,6 +228,36 @@
   </si>
   <si>
     <t>Recibo do pagamento ajuste</t>
+  </si>
+  <si>
+    <t>NÃO</t>
+  </si>
+  <si>
+    <t>VENCIDO_venc:30/04/2026</t>
+  </si>
+  <si>
+    <t>SÃO BENTO</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO 001/2025</t>
+  </si>
+  <si>
+    <t>Cobrança indevida - Perdas nos reatores</t>
+  </si>
+  <si>
+    <t>Cobrança indevida UC 209296</t>
+  </si>
+  <si>
+    <t>Pendente fazer relatório de pagamento</t>
+  </si>
+  <si>
+    <t>Débora</t>
+  </si>
+  <si>
+    <t>010.601.50025-06</t>
+  </si>
+  <si>
+    <t>Concluída</t>
   </si>
 </sst>
 </file>
@@ -276,7 +267,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,18 +328,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C5700"/>
+      <color rgb="FF275317"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF275317"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE97132"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,18 +384,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFBE2D5"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -483,24 +486,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -520,7 +510,32 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -529,73 +544,54 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -622,6 +618,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -906,17 +905,19 @@
   <dimension ref="A1:BA12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="17" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="18.44140625" bestFit="1" customWidth="1"/>
@@ -943,141 +944,141 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="36" t="s">
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="39" t="s">
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="40"/>
-      <c r="AK1" s="40"/>
-      <c r="AL1" s="40"/>
-      <c r="AM1" s="40"/>
-      <c r="AN1" s="41" t="s">
+      <c r="AH1" s="42"/>
+      <c r="AI1" s="42"/>
+      <c r="AJ1" s="42"/>
+      <c r="AK1" s="42"/>
+      <c r="AL1" s="42"/>
+      <c r="AM1" s="42"/>
+      <c r="AN1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="43"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
     </row>
     <row r="2" spans="1:53" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="9" t="s">
         <v>18</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="20" t="s">
+      <c r="S2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="T2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="20" t="s">
+      <c r="U2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="22" t="s">
+      <c r="V2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="20" t="s">
+      <c r="W2" s="10" t="s">
         <v>27</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="Y2" s="21" t="s">
+      <c r="Y2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="Z2" s="21" t="s">
+      <c r="Z2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AA2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AB2" s="21" t="s">
+      <c r="AB2" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AC2" s="21" t="s">
+      <c r="AC2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AD2" s="21" t="s">
+      <c r="AD2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="AE2" s="21" t="s">
+      <c r="AE2" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="AF2" s="21" t="s">
+      <c r="AF2" s="11" t="s">
         <v>36</v>
       </c>
       <c r="AG2" s="6" t="s">
@@ -1101,41 +1102,41 @@
       <c r="AM2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AN2" s="19" t="s">
+      <c r="AN2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="19" t="s">
+      <c r="AO2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AP2" s="19" t="s">
+      <c r="AP2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AQ2" s="18" t="s">
+      <c r="AQ2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AR2" s="19" t="s">
+      <c r="AR2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AS2" s="18" t="s">
+      <c r="AS2" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:53" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
       <c r="P3" s="4" t="s">
         <v>20</v>
       </c>
@@ -1144,7 +1145,7 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
-      <c r="V3" s="23"/>
+      <c r="V3" s="13"/>
       <c r="W3" s="3"/>
       <c r="X3" s="5" t="s">
         <v>28</v>
@@ -1172,195 +1173,183 @@
         <v>37</v>
       </c>
       <c r="AM3" s="6"/>
-      <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
-      <c r="AP3" s="19"/>
-      <c r="AQ3" s="18"/>
-      <c r="AR3" s="19"/>
-      <c r="AS3" s="18"/>
-      <c r="AT3" s="18" t="s">
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AU3" s="18" t="s">
+      <c r="AV3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AV3" s="18" t="s">
+      <c r="AW3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="AW3" s="18" t="s">
+      <c r="AX3" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="AX3" s="18" t="s">
+      <c r="AY3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="AY3" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ3" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA3" s="18" t="s">
-        <v>76</v>
+      <c r="AZ3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="BA3" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:53" s="28" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:53" s="14" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="B4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="E4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="F4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="11">
-        <v>45848</v>
-      </c>
-      <c r="K4" s="10">
-        <v>46066</v>
-      </c>
-      <c r="L4" s="25">
-        <v>40797.14</v>
-      </c>
-      <c r="M4" s="11">
-        <v>46077</v>
-      </c>
-      <c r="N4" s="25">
-        <v>40797.14</v>
-      </c>
-      <c r="O4" s="12">
+      <c r="G4" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="19">
+        <v>209296</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="20">
+        <v>45793</v>
+      </c>
+      <c r="K4" s="20">
+        <v>46104</v>
+      </c>
+      <c r="L4" s="21">
+        <v>9650.57</v>
+      </c>
+      <c r="M4" s="22">
+        <v>46101</v>
+      </c>
+      <c r="N4" s="23">
+        <v>9650.57</v>
+      </c>
+      <c r="O4" s="24">
         <v>1</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>45839</v>
-      </c>
-      <c r="R4" s="14">
-        <v>186730368</v>
-      </c>
-      <c r="S4" s="13">
-        <v>45848</v>
-      </c>
-      <c r="T4" s="13">
-        <v>45846</v>
-      </c>
-      <c r="U4" s="26" t="s">
+      <c r="P4" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q4" s="26">
+        <v>45793</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="S4" s="26">
+        <v>45793</v>
+      </c>
+      <c r="T4" s="26">
+        <v>45800</v>
+      </c>
+      <c r="U4" s="28" t="s">
         <v>52</v>
       </c>
       <c r="V4" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="W4" s="24" t="s">
+      <c r="W4" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="X4" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" s="26">
+        <v>45966</v>
+      </c>
+      <c r="Z4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA4" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC4" s="26">
+        <v>45980</v>
+      </c>
+      <c r="AD4" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE4" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF4" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="X4" s="16" t="s">
+      <c r="AG4" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" s="13">
-        <v>45930</v>
-      </c>
-      <c r="Z4" s="7" t="s">
+      <c r="AH4" s="26">
+        <v>45993</v>
+      </c>
+      <c r="AI4" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ4" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK4" s="26">
+        <v>46132</v>
+      </c>
+      <c r="AL4" s="26">
+        <v>46132</v>
+      </c>
+      <c r="AM4" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="AA4" s="16" t="s">
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AQ4" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="AC4" s="13">
-        <v>45944</v>
-      </c>
-      <c r="AD4" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE4" s="15" t="s">
+      <c r="AR4" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="AF4" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG4" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" s="13">
-        <v>45967</v>
-      </c>
-      <c r="AI4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ4" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK4" s="13">
-        <v>46156</v>
-      </c>
-      <c r="AL4" s="7" t="s">
+      <c r="AS4" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="AM4" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN4" s="15"/>
-      <c r="AO4" s="15"/>
-      <c r="AP4" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ4" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AR4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AS4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="AT4" s="13">
-        <v>46080</v>
-      </c>
-      <c r="AU4" s="7"/>
-      <c r="AV4" s="25">
-        <v>23029.01</v>
-      </c>
-      <c r="AW4" s="11">
-        <v>46153</v>
-      </c>
-      <c r="AX4" s="13">
-        <v>46182</v>
-      </c>
-      <c r="AY4" s="25">
-        <v>1406.68</v>
-      </c>
-      <c r="AZ4" s="13">
-        <v>46185</v>
-      </c>
-      <c r="BA4" s="13">
-        <v>46191</v>
-      </c>
+      <c r="AT4" s="44">
+        <v>46104</v>
+      </c>
+      <c r="AU4" s="34"/>
+      <c r="AV4" s="34"/>
+      <c r="AW4" s="34"/>
+      <c r="AX4" s="34"/>
+      <c r="AY4" s="34"/>
+      <c r="AZ4" s="34"/>
+      <c r="BA4" s="34"/>
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.3">
-      <c r="N12" s="17"/>
-      <c r="Q12" s="17"/>
+      <c r="N12" s="7"/>
+      <c r="Q12" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Tabela.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Tabela.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750D7CEE-91D0-42F6-A62E-755D92A36194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F1A620-9211-4721-9182-0988CAD71909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
   <si>
     <t>CONCESSIONÁRIA - 1º NIVEL</t>
   </si>
@@ -185,79 +185,91 @@
     <t>NF's</t>
   </si>
   <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>Brena</t>
+  </si>
+  <si>
+    <t>Deferido</t>
+  </si>
+  <si>
+    <t>S/I</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Comprovante de pagamento</t>
+  </si>
+  <si>
+    <t>Memorial Corrigido</t>
+  </si>
+  <si>
+    <t>Valor Complementar</t>
+  </si>
+  <si>
+    <t>Data do pagamento complementar</t>
+  </si>
+  <si>
+    <t>Recibo do pagamento complementar</t>
+  </si>
+  <si>
+    <t>Valor ajuste</t>
+  </si>
+  <si>
+    <t>Data do pagamento ajuste</t>
+  </si>
+  <si>
+    <t>Recibo do pagamento ajuste</t>
+  </si>
+  <si>
+    <t>NÃO</t>
+  </si>
+  <si>
     <t>THAMIRES E RUDÁ</t>
   </si>
   <si>
-    <t>PB</t>
-  </si>
-  <si>
-    <t>Brena</t>
-  </si>
-  <si>
-    <t>Deferido</t>
-  </si>
-  <si>
-    <t>S/I</t>
-  </si>
-  <si>
-    <t>Aguardando cálculo</t>
-  </si>
-  <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>Comprovante de pagamento</t>
-  </si>
-  <si>
-    <t>Memorial Corrigido</t>
-  </si>
-  <si>
-    <t>Valor Complementar</t>
-  </si>
-  <si>
-    <t>Data do pagamento complementar</t>
-  </si>
-  <si>
-    <t>Recibo do pagamento complementar</t>
-  </si>
-  <si>
-    <t>Valor ajuste</t>
-  </si>
-  <si>
-    <t>Data do pagamento ajuste</t>
-  </si>
-  <si>
-    <t>Recibo do pagamento ajuste</t>
-  </si>
-  <si>
-    <t>NÃO</t>
-  </si>
-  <si>
-    <t>VENCIDO_venc:30/04/2026</t>
-  </si>
-  <si>
-    <t>SÃO BENTO</t>
-  </si>
-  <si>
-    <t>RECLAMAÇÃO 001/2025</t>
+    <t>Respondido</t>
+  </si>
+  <si>
+    <t>VIGENTE_venc:16/12/2026</t>
+  </si>
+  <si>
+    <t>CAPIM</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO 010/2025</t>
   </si>
   <si>
     <t>Cobrança indevida - Perdas nos reatores</t>
   </si>
   <si>
-    <t>Cobrança indevida UC 209296</t>
-  </si>
-  <si>
-    <t>Pendente fazer relatório de pagamento</t>
+    <t>Cobrança indevida UC 720837</t>
+  </si>
+  <si>
+    <t>Concluído</t>
   </si>
   <si>
     <t>Débora</t>
   </si>
   <si>
-    <t>010.601.50025-06</t>
-  </si>
-  <si>
-    <t>Concluída</t>
+    <t>Reeingressado por conta de pendência</t>
+  </si>
+  <si>
+    <t>010.586.34725-64</t>
+  </si>
+  <si>
+    <t>Contestar</t>
+  </si>
+  <si>
+    <t>O memorial de cálculo foi contestado, pois faltava uma parte do dobro, no protocolo 010.631.53326-25</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Relatório enviado ao parceiro</t>
   </si>
 </sst>
 </file>
@@ -267,7 +279,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,29 +308,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0D0D0D"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,24 +317,25 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF275317"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFE97132"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,24 +374,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFCCCCFF"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FF3C7D22"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE2D5"/>
+        <fgColor rgb="FF8ED973"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94DCF8"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -486,11 +482,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -510,7 +519,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -532,66 +541,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -618,9 +615,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -902,33 +896,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA12"/>
+  <dimension ref="A1:BB12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -944,47 +939,47 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="35" t="s">
+      <c r="P1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="38" t="s">
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="40"/>
-      <c r="AG1" s="41" t="s">
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="42"/>
-      <c r="AI1" s="42"/>
-      <c r="AJ1" s="42"/>
-      <c r="AK1" s="42"/>
-      <c r="AL1" s="42"/>
-      <c r="AM1" s="42"/>
-      <c r="AN1" s="43" t="s">
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
+      <c r="AK1" s="38"/>
+      <c r="AL1" s="38"/>
+      <c r="AM1" s="38"/>
+      <c r="AN1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="43"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
     </row>
-    <row r="2" spans="1:53" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -1121,7 +1116,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="8"/>
@@ -1180,44 +1175,44 @@
       <c r="AR3" s="9"/>
       <c r="AS3" s="8"/>
       <c r="AT3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="AV3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AU3" s="8" t="s">
+      <c r="AW3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="AX3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="AZ3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="BA3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:54" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="1:53" s="14" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>66</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>67</v>
       </c>
       <c r="F4" s="17" t="s">
@@ -1227,127 +1222,136 @@
         <v>69</v>
       </c>
       <c r="H4" s="19">
-        <v>209296</v>
-      </c>
-      <c r="I4" s="16" t="s">
+        <v>720837</v>
+      </c>
+      <c r="I4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="20">
-        <v>45793</v>
-      </c>
-      <c r="K4" s="20">
-        <v>46104</v>
-      </c>
-      <c r="L4" s="21">
-        <v>9650.57</v>
-      </c>
-      <c r="M4" s="22">
-        <v>46101</v>
-      </c>
-      <c r="N4" s="23">
-        <v>9650.57</v>
-      </c>
-      <c r="O4" s="24">
+      <c r="J4" s="21">
+        <v>45796</v>
+      </c>
+      <c r="K4" s="21">
+        <v>45796</v>
+      </c>
+      <c r="L4" s="22">
+        <v>79188.820000000007</v>
+      </c>
+      <c r="M4" s="23">
+        <v>45800</v>
+      </c>
+      <c r="N4" s="24">
+        <v>79188.820000000007</v>
+      </c>
+      <c r="O4" s="25">
         <v>1</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="P4" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="Q4" s="26">
-        <v>45793</v>
-      </c>
-      <c r="R4" s="27" t="s">
+      <c r="Q4" s="23">
+        <v>45754</v>
+      </c>
+      <c r="R4" s="15">
+        <v>183037563</v>
+      </c>
+      <c r="S4" s="23">
+        <v>45796</v>
+      </c>
+      <c r="T4" s="23">
+        <v>45761</v>
+      </c>
+      <c r="U4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="26">
-        <v>45793</v>
-      </c>
-      <c r="T4" s="26">
-        <v>45800</v>
-      </c>
-      <c r="U4" s="28" t="s">
+      <c r="X4" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y4" s="23">
+        <v>45772</v>
+      </c>
+      <c r="Z4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="V4" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="W4" s="29" t="s">
+      <c r="AA4" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB4" s="23">
+        <v>45789</v>
+      </c>
+      <c r="AC4" s="23">
+        <v>45802</v>
+      </c>
+      <c r="AD4" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y4" s="26">
-        <v>45966</v>
-      </c>
-      <c r="Z4" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA4" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB4" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC4" s="26">
-        <v>45980</v>
-      </c>
-      <c r="AD4" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE4" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF4" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="AG4" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH4" s="26">
-        <v>45993</v>
+      <c r="AE4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF4" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" s="23">
+        <v>45904</v>
       </c>
       <c r="AI4" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ4" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="AK4" s="26">
-        <v>46132</v>
-      </c>
-      <c r="AL4" s="26">
-        <v>46132</v>
-      </c>
-      <c r="AM4" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="AN4" s="30"/>
-      <c r="AO4" s="30"/>
-      <c r="AP4" s="34" t="s">
-        <v>53</v>
+      <c r="AJ4" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK4" s="23">
+        <v>46126</v>
+      </c>
+      <c r="AL4" s="23">
+        <v>46126</v>
+      </c>
+      <c r="AM4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="29" t="s">
+        <v>52</v>
       </c>
       <c r="AQ4" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR4" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS4" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT4" s="44">
-        <v>46104</v>
-      </c>
-      <c r="AU4" s="34"/>
-      <c r="AV4" s="34"/>
-      <c r="AW4" s="34"/>
-      <c r="AX4" s="34"/>
-      <c r="AY4" s="34"/>
-      <c r="AZ4" s="34"/>
-      <c r="BA4" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="AR4" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS4" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT4" s="23">
+        <v>45803</v>
+      </c>
+      <c r="AU4" s="23">
+        <v>46171</v>
+      </c>
+      <c r="AV4" s="24">
+        <v>7139.04</v>
+      </c>
+      <c r="AW4" s="23">
+        <v>46168</v>
+      </c>
+      <c r="AX4" s="23">
+        <v>46171</v>
+      </c>
+      <c r="AY4" s="15"/>
+      <c r="AZ4" s="15"/>
+      <c r="BA4" s="15"/>
+      <c r="BB4" s="30"/>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
       <c r="N12" s="7"/>
       <c r="Q12" s="7"/>
     </row>

--- a/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Tabela.xlsx
+++ b/02 - DOCUMENTOS/RELATÓRIO DE PAGAMENTO/Tabela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\02 - DOCUMENTOS\RELATÓRIO DE PAGAMENTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F1A620-9211-4721-9182-0988CAD71909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584A68D6-ED6F-4A82-9144-9896052CB41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
   <si>
     <t>CONCESSIONÁRIA - 1º NIVEL</t>
   </si>
@@ -224,52 +224,49 @@
     <t>Recibo do pagamento ajuste</t>
   </si>
   <si>
+    <t>THAMIRES E RUDÁ</t>
+  </si>
+  <si>
+    <t>Cobrança indevida</t>
+  </si>
+  <si>
+    <t>Aguardando cálculo</t>
+  </si>
+  <si>
+    <t>Sem resposta</t>
+  </si>
+  <si>
+    <t>Passar para próxima instância</t>
+  </si>
+  <si>
+    <t>VIGENTE_venc:13/05/2027</t>
+  </si>
+  <si>
+    <t>SÃO JOSÉ DE SABUGI</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO 028/2025</t>
+  </si>
+  <si>
+    <t>Cobrança indevida - Perdas nos reatores</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
     <t>NÃO</t>
   </si>
   <si>
-    <t>THAMIRES E RUDÁ</t>
-  </si>
-  <si>
-    <t>Respondido</t>
-  </si>
-  <si>
-    <t>VIGENTE_venc:16/12/2026</t>
-  </si>
-  <si>
-    <t>CAPIM</t>
-  </si>
-  <si>
-    <t>RECLAMAÇÃO 010/2025</t>
-  </si>
-  <si>
-    <t>Cobrança indevida - Perdas nos reatores</t>
-  </si>
-  <si>
-    <t>Cobrança indevida UC 720837</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>Débora</t>
-  </si>
-  <si>
-    <t>Reeingressado por conta de pendência</t>
-  </si>
-  <si>
-    <t>010.586.34725-64</t>
+    <t>010.597.10325-61</t>
+  </si>
+  <si>
+    <t>Concluída</t>
   </si>
   <si>
     <t>Contestar</t>
   </si>
   <si>
-    <t>O memorial de cálculo foi contestado, pois faltava uma parte do dobro, no protocolo 010.631.53326-25</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Relatório enviado ao parceiro</t>
+    <t>Solicitação devolução complementar do dobro feita na ouvidoria da ANEEL. Valor pendente: R$ 7.413,62</t>
   </si>
 </sst>
 </file>
@@ -279,7 +276,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,25 +314,53 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7030A0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF275317"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -380,19 +405,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF8ED973"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF262626"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF3C7D22"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8ED973"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94DCF8"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
@@ -499,7 +536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -541,52 +578,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -615,6 +652,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1201,155 +1250,157 @@
     </row>
     <row r="4" spans="1:54" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="19">
-        <v>720837</v>
-      </c>
-      <c r="I4" s="20" t="s">
+      <c r="F4" s="18" t="s">
         <v>70</v>
       </c>
+      <c r="G4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="20">
+        <v>260328</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>71</v>
+      </c>
       <c r="J4" s="21">
-        <v>45796</v>
+        <v>45903</v>
       </c>
       <c r="K4" s="21">
-        <v>45796</v>
+        <v>46073</v>
       </c>
       <c r="L4" s="22">
-        <v>79188.820000000007</v>
+        <v>24999.26</v>
       </c>
       <c r="M4" s="23">
-        <v>45800</v>
+        <v>46078</v>
       </c>
       <c r="N4" s="24">
-        <v>79188.820000000007</v>
+        <v>24999.26</v>
       </c>
       <c r="O4" s="25">
         <v>1</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="23">
-        <v>45754</v>
-      </c>
-      <c r="R4" s="15">
-        <v>183037563</v>
+        <v>45897</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>52</v>
       </c>
       <c r="S4" s="23">
-        <v>45796</v>
+        <v>45903</v>
       </c>
       <c r="T4" s="23">
-        <v>45761</v>
-      </c>
-      <c r="U4" s="26" t="s">
+        <v>45904</v>
+      </c>
+      <c r="U4" s="28" t="s">
         <v>51</v>
       </c>
       <c r="V4" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="W4" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="W4" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="X4" s="27" t="s">
-        <v>71</v>
+      <c r="X4" s="29" t="s">
+        <v>50</v>
       </c>
       <c r="Y4" s="23">
-        <v>45772</v>
+        <v>45922</v>
       </c>
       <c r="Z4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="AA4" s="27" t="s">
+      <c r="AA4" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AB4" s="23">
-        <v>45789</v>
+      <c r="AB4" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="AC4" s="23">
-        <v>45802</v>
-      </c>
-      <c r="AD4" s="28" t="s">
-        <v>64</v>
+        <v>45936</v>
+      </c>
+      <c r="AD4" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="AE4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF4" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG4" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>50</v>
       </c>
       <c r="AH4" s="23">
-        <v>45904</v>
+        <v>45967</v>
       </c>
       <c r="AI4" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="AJ4" s="28" t="s">
-        <v>64</v>
+      <c r="AJ4" s="42" t="s">
+        <v>74</v>
       </c>
       <c r="AK4" s="23">
-        <v>46126</v>
+        <v>46108</v>
       </c>
       <c r="AL4" s="23">
-        <v>46126</v>
+        <v>46108</v>
       </c>
       <c r="AM4" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN4" s="15"/>
-      <c r="AO4" s="15"/>
-      <c r="AP4" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN4" s="26" t="s">
         <v>52</v>
       </c>
+      <c r="AO4" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="AP4" s="26" t="s">
+        <v>52</v>
+      </c>
       <c r="AQ4" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AR4" s="15" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="AS4" s="15" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="AT4" s="23">
-        <v>45803</v>
-      </c>
-      <c r="AU4" s="23">
-        <v>46171</v>
-      </c>
-      <c r="AV4" s="24">
-        <v>7139.04</v>
+        <v>46101</v>
+      </c>
+      <c r="AU4" s="26"/>
+      <c r="AV4" s="22">
+        <v>8104.11</v>
       </c>
       <c r="AW4" s="23">
-        <v>46168</v>
+        <v>46191</v>
       </c>
       <c r="AX4" s="23">
-        <v>46171</v>
-      </c>
-      <c r="AY4" s="15"/>
-      <c r="AZ4" s="15"/>
-      <c r="BA4" s="15"/>
-      <c r="BB4" s="30"/>
+        <v>46218</v>
+      </c>
+      <c r="AY4" s="26"/>
+      <c r="AZ4" s="26"/>
+      <c r="BA4" s="26"/>
+      <c r="BB4" s="43"/>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.3">
       <c r="N12" s="7"/>
